--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.95141586019504</v>
+        <v>12.5046050772817</v>
       </c>
       <c r="D2" t="n">
-        <v>42.46137848468143</v>
+        <v>6.899974003760732</v>
       </c>
       <c r="E2" t="n">
-        <v>2.861485068941427</v>
+        <v>0.4649913237029821</v>
       </c>
       <c r="F2" t="n">
-        <v>4.83849354467241</v>
+        <v>0.7862552010092672</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>71.22844572231219</v>
+        <v>11.57462242987573</v>
       </c>
       <c r="D3" t="n">
-        <v>52.13836557402625</v>
+        <v>8.472484405779266</v>
       </c>
       <c r="E3" t="n">
-        <v>2.861485068941427</v>
+        <v>0.4649913237029821</v>
       </c>
       <c r="F3" t="n">
-        <v>4.83849354467241</v>
+        <v>0.7862552010092672</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
